--- a/whiskeyjack-bot-v1-backlog.xlsx
+++ b/whiskeyjack-bot-v1-backlog.xlsx
@@ -788,7 +788,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -1635,7 +1634,7 @@
       </c>
       <c r="J18" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K18" s="32" t="inlineStr">
@@ -1692,7 +1691,7 @@
       </c>
       <c r="J19" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="K19" s="32" t="inlineStr">

--- a/whiskeyjack-bot-v1-backlog.xlsx
+++ b/whiskeyjack-bot-v1-backlog.xlsx
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J16" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="K16" s="32" t="inlineStr">

--- a/whiskeyjack-bot-v1-backlog.xlsx
+++ b/whiskeyjack-bot-v1-backlog.xlsx
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J16" s="31" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K16" s="32" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="J17" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="K17" s="32" t="inlineStr">

--- a/whiskeyjack-bot-v1-backlog.xlsx
+++ b/whiskeyjack-bot-v1-backlog.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="J15" s="31" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K15" s="32" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="J17" s="31" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K17" s="32" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J18" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K18" s="32" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J19" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="K19" s="32" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="J22" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="K22" s="32" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="J24" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K24" s="32" t="inlineStr">
